--- a/backend/uploads/excel/69aa8af0ff0503c3e2a7cb2a_drawings.xlsx
+++ b/backend/uploads/excel/69aa8af0ff0503c3e2a7cb2a_drawings.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="158">
   <si>
     <t>Sl. No.</t>
   </si>
@@ -897,7 +897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3243,6 +3243,29 @@
         <v>141</v>
       </c>
     </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="3">
+        <v>101</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
